--- a/Excel/025-Buy Sell Targets.xlsx
+++ b/Excel/025-Buy Sell Targets.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_6DC67CE604957413C1C00D30244B3202AF4C935C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B29C6FB-BF36-47AA-8BBE-26DE331B7436}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_6DC67CE670ED77F273E5644EB82B149C87549D71" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B977AA0-4090-43A9-A4F6-9D124B863C5E}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="156" yWindow="288" windowWidth="12552" windowHeight="10272" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10800" yWindow="1200" windowWidth="11508" windowHeight="10872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <si>
     <t>Name</t>
   </si>
@@ -83,6 +86,9 @@
     <t>GVREIT</t>
   </si>
   <si>
+    <t>IVL</t>
+  </si>
+  <si>
     <t>PROSPECT</t>
   </si>
   <si>
@@ -98,6 +104,9 @@
     <t>TOA</t>
   </si>
   <si>
+    <t>PTG</t>
+  </si>
+  <si>
     <t>Sell</t>
   </si>
   <si>
@@ -125,7 +134,42 @@
     <t>TVO</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">HOLD </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>ยท</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> TREND UP</t>
+    </r>
+  </si>
+  <si>
     <t>WHAIR</t>
+  </si>
+  <si>
+    <t>ORI</t>
+  </si>
+  <si>
+    <t>Short Sales</t>
+  </si>
+  <si>
+    <t>Pending</t>
   </si>
 </sst>
 </file>
@@ -133,30 +177,37 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="#,##0_ "/>
-    <numFmt numFmtId="165" formatCode="[$฿-41E]#,##0.00;\-[$฿-41E]#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0000_ "/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="168" formatCode="[$฿-41E]#,##0.00"/>
+    <numFmt numFmtId="187" formatCode="#,##0_ "/>
+    <numFmt numFmtId="188" formatCode="[$฿-41E]#,##0.00;\-[$฿-41E]#,##0.00"/>
+    <numFmt numFmtId="189" formatCode="0.0000_ "/>
+    <numFmt numFmtId="190" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="191" formatCode="[$฿-41E]#,##0.00"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -164,21 +215,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -189,8 +233,8 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
@@ -200,17 +244,28 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
-      <name val="Segoe UI"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -233,58 +288,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="190" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -300,10 +348,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -584,94 +628,95 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" customWidth="1"/>
-    <col min="3" max="3" width="9" style="5"/>
-    <col min="4" max="4" width="11.21875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="10" style="6" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="10" style="7" customWidth="1"/>
-    <col min="11" max="11" width="7.44140625" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.09765625" customWidth="1"/>
+    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="3" max="3" width="7.3984375" style="6" customWidth="1"/>
+    <col min="4" max="4" width="11.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.09765625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" style="8" customWidth="1"/>
+    <col min="11" max="11" width="7.3984375" customWidth="1"/>
+    <col min="12" max="12" width="15.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="46" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="48" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="46" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="46" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="46" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="50" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="19">
         <v>320</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="20">
         <v>100</v>
       </c>
-      <c r="D2" s="16">
-        <f t="shared" ref="D2:D6" si="0">B2*C2</f>
+      <c r="D2" s="21">
+        <f>B2*C2</f>
         <v>32000</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="21">
         <v>355</v>
       </c>
-      <c r="F2" s="38">
+      <c r="F2" s="20">
         <v>400</v>
       </c>
-      <c r="G2" s="17">
-        <f t="shared" ref="G2:G6" si="1">E2*F2</f>
+      <c r="G2" s="22">
+        <f>E2*F2</f>
         <v>142000</v>
       </c>
-      <c r="H2" s="15">
-        <f t="shared" ref="H2:I5" si="2">C2+F2</f>
+      <c r="H2" s="20">
+        <f t="shared" ref="H2:I5" si="0">C2+F2</f>
         <v>500</v>
       </c>
-      <c r="I2" s="17">
-        <f t="shared" si="2"/>
+      <c r="I2" s="22">
+        <f t="shared" si="0"/>
         <v>174000</v>
       </c>
-      <c r="J2" s="31">
-        <f t="shared" ref="J2:J6" si="3">I2/H2</f>
+      <c r="J2" s="36">
+        <f>I2/H2</f>
         <v>348</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="3">
         <v>355.75</v>
       </c>
     </row>
@@ -679,36 +724,36 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="13">
         <v>14</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="6">
         <v>1200</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="7">
+        <f>B3*C3</f>
+        <v>16800</v>
+      </c>
+      <c r="E3" s="7">
+        <v>37</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1200</v>
+      </c>
+      <c r="G3" s="14">
+        <f>E3*F3</f>
+        <v>44400</v>
+      </c>
+      <c r="H3" s="6">
         <f t="shared" si="0"/>
-        <v>16800</v>
-      </c>
-      <c r="E3" s="6">
-        <v>37</v>
-      </c>
-      <c r="F3" s="37">
-        <v>1200</v>
-      </c>
-      <c r="G3" s="13">
-        <f t="shared" si="1"/>
-        <v>44400</v>
-      </c>
-      <c r="H3" s="5">
-        <f t="shared" si="2"/>
         <v>2400</v>
       </c>
-      <c r="I3" s="13">
-        <f t="shared" si="2"/>
+      <c r="I3" s="14">
+        <f t="shared" si="0"/>
         <v>61200</v>
       </c>
-      <c r="J3" s="7">
-        <f t="shared" si="3"/>
+      <c r="J3" s="8">
+        <f>I3/H3</f>
         <v>25.5</v>
       </c>
       <c r="K3">
@@ -719,523 +764,680 @@
       <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="13">
         <v>2.44</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="6">
         <v>9000</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="7">
+        <f>B4*C4</f>
+        <v>21960</v>
+      </c>
+      <c r="E4" s="7">
+        <v>4.96</v>
+      </c>
+      <c r="F4" s="6">
+        <v>9000</v>
+      </c>
+      <c r="G4" s="14">
+        <f>E4*F4</f>
+        <v>44640</v>
+      </c>
+      <c r="H4" s="6">
         <f t="shared" si="0"/>
-        <v>21960</v>
-      </c>
-      <c r="E4" s="6">
-        <v>4.96</v>
-      </c>
-      <c r="F4" s="37">
-        <v>9000</v>
-      </c>
-      <c r="G4" s="13">
-        <f t="shared" si="1"/>
-        <v>44640</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" si="2"/>
         <v>18000</v>
       </c>
-      <c r="I4" s="13">
-        <f t="shared" si="2"/>
+      <c r="I4" s="14">
+        <f t="shared" si="0"/>
         <v>66600</v>
       </c>
-      <c r="J4" s="7">
-        <f t="shared" si="3"/>
+      <c r="J4" s="8">
+        <f>I4/H4</f>
         <v>3.7</v>
       </c>
       <c r="K4">
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="12">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="B5" s="15">
+        <v>10.9</v>
+      </c>
+      <c r="C5" s="16">
         <v>2000</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="17">
+        <f>B5*C5</f>
+        <v>21800</v>
+      </c>
+      <c r="E5" s="17">
+        <v>21.7</v>
+      </c>
+      <c r="F5" s="16">
+        <v>4000</v>
+      </c>
+      <c r="G5" s="18">
+        <f>E5*F5</f>
+        <v>86800</v>
+      </c>
+      <c r="H5" s="16">
         <f t="shared" si="0"/>
-        <v>20000</v>
-      </c>
-      <c r="E5" s="6">
-        <v>21.7</v>
-      </c>
-      <c r="F5" s="37">
-        <v>4000</v>
-      </c>
-      <c r="G5" s="13">
-        <f t="shared" si="1"/>
-        <v>86800</v>
-      </c>
-      <c r="H5" s="5">
-        <f t="shared" si="2"/>
         <v>6000</v>
       </c>
-      <c r="I5" s="13">
-        <f t="shared" si="2"/>
-        <v>106800</v>
-      </c>
-      <c r="J5" s="7">
-        <f t="shared" si="3"/>
-        <v>17.8</v>
-      </c>
-      <c r="K5">
+      <c r="I5" s="18">
+        <f t="shared" si="0"/>
+        <v>108600</v>
+      </c>
+      <c r="J5" s="35">
+        <f>I5/H5</f>
+        <v>18.100000000000001</v>
+      </c>
+      <c r="K5" s="2">
         <v>13.96</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="15">
+        <v>7.85</v>
+      </c>
+      <c r="C6" s="16">
+        <v>2400</v>
+      </c>
+      <c r="D6" s="17">
+        <f>B6*C6</f>
+        <v>18840</v>
+      </c>
+      <c r="E6" s="17">
+        <v>11.4</v>
+      </c>
+      <c r="F6" s="16">
+        <v>3600</v>
+      </c>
+      <c r="G6" s="18">
+        <f>E6*F6</f>
+        <v>41040</v>
+      </c>
+      <c r="H6" s="16">
+        <f>C6+F6</f>
+        <v>6000</v>
+      </c>
+      <c r="I6" s="18">
+        <f>D6+G6</f>
+        <v>59880</v>
+      </c>
+      <c r="J6" s="35">
+        <f>I6/H6</f>
+        <v>9.98</v>
+      </c>
+      <c r="K6" s="2">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="8">
-        <v>6.75</v>
-      </c>
-      <c r="C6" s="9">
-        <v>8000</v>
-      </c>
-      <c r="D6" s="10">
-        <f t="shared" si="0"/>
-        <v>54000</v>
-      </c>
-      <c r="E6" s="10">
-        <v>7.75</v>
-      </c>
-      <c r="F6" s="36">
-        <v>72000</v>
-      </c>
-      <c r="G6" s="11">
-        <f t="shared" si="1"/>
-        <v>558000</v>
-      </c>
-      <c r="H6" s="9">
-        <f>C6+F6</f>
-        <v>80000</v>
-      </c>
-      <c r="I6" s="11">
-        <f>D6+G6</f>
-        <v>612000</v>
-      </c>
-      <c r="J6" s="30">
-        <f t="shared" si="3"/>
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="8">
-        <v>8.75</v>
-      </c>
-      <c r="C7" s="9">
-        <v>5000</v>
-      </c>
-      <c r="D7" s="10">
-        <f>B7*C7</f>
-        <v>43750</v>
-      </c>
-      <c r="E7" s="10">
+      <c r="B7" s="13">
+        <v>7.2</v>
+      </c>
+      <c r="C7" s="6">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="19">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="C8" s="20">
+        <v>2500</v>
+      </c>
+      <c r="D8" s="21">
+        <f t="shared" ref="D8:D12" si="1">B8*C8</f>
+        <v>22000</v>
+      </c>
+      <c r="E8" s="21">
         <v>9.6</v>
       </c>
-      <c r="F7" s="36">
+      <c r="F8" s="20">
         <v>37500</v>
       </c>
-      <c r="G7" s="11">
-        <f>E7*F7</f>
+      <c r="G8" s="22">
+        <f t="shared" ref="G8:G12" si="2">E8*F8</f>
         <v>360000</v>
       </c>
-      <c r="H7" s="9">
-        <f>C7+F7</f>
-        <v>42500</v>
-      </c>
-      <c r="I7" s="11">
-        <f>D7+G7</f>
-        <v>403750</v>
-      </c>
-      <c r="J7" s="30">
-        <f>I7/H7</f>
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="12">
-        <v>10.4</v>
-      </c>
-      <c r="C8" s="5">
-        <v>3000</v>
-      </c>
-      <c r="F8" s="37"/>
+      <c r="H8" s="20">
+        <f>C8+F8</f>
+        <v>40000</v>
+      </c>
+      <c r="I8" s="22">
+        <f>D8+G8</f>
+        <v>382000</v>
+      </c>
+      <c r="J8" s="36">
+        <f t="shared" ref="J8:J12" si="3">I8/H8</f>
+        <v>9.5500000000000007</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="13">
+        <v>10.4</v>
+      </c>
+      <c r="C9" s="6">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="13">
         <v>9.1999999999999993</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C10" s="6">
         <v>2500</v>
       </c>
-      <c r="D9" s="6">
-        <f>B9*C9</f>
+      <c r="D10" s="7">
+        <f t="shared" si="1"/>
         <v>23000</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E10" s="7">
         <v>26.4</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F10" s="6">
         <v>17500</v>
       </c>
-      <c r="G9" s="13">
-        <f>E9*F9</f>
+      <c r="G10" s="14">
+        <f t="shared" si="2"/>
         <v>462000</v>
       </c>
-      <c r="H9" s="5">
-        <f t="shared" ref="H9:I11" si="4">C9+F9</f>
+      <c r="H10" s="6">
+        <f t="shared" ref="H10:I12" si="4">C10+F10</f>
         <v>20000</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I10" s="14">
         <f t="shared" si="4"/>
         <v>485000</v>
       </c>
-      <c r="J9" s="7">
-        <f>I9/H9</f>
+      <c r="J10" s="8">
+        <f t="shared" si="3"/>
         <v>24.25</v>
       </c>
-      <c r="K9">
+      <c r="K10">
         <v>9.66</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="8">
-        <v>6.8</v>
-      </c>
-      <c r="C10" s="9">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="13">
+        <v>6.9</v>
+      </c>
+      <c r="C11" s="6">
         <v>5000</v>
       </c>
-      <c r="D10" s="10">
-        <f>B10*C10</f>
-        <v>34000</v>
-      </c>
-      <c r="E10" s="10">
+      <c r="D11" s="7">
+        <f t="shared" si="1"/>
+        <v>34500</v>
+      </c>
+      <c r="E11" s="7">
+        <v>7.25</v>
+      </c>
+      <c r="F11" s="6">
+        <v>30000</v>
+      </c>
+      <c r="G11" s="14">
+        <f t="shared" si="2"/>
+        <v>217500</v>
+      </c>
+      <c r="H11" s="6">
+        <f t="shared" si="4"/>
+        <v>35000</v>
+      </c>
+      <c r="I11" s="14">
+        <f t="shared" si="4"/>
+        <v>252000</v>
+      </c>
+      <c r="J11" s="8">
+        <f t="shared" si="3"/>
         <v>7.2</v>
       </c>
-      <c r="F10" s="36">
-        <v>35000</v>
-      </c>
-      <c r="G10" s="11">
-        <f>E10*F10</f>
-        <v>252000</v>
-      </c>
-      <c r="H10" s="9">
-        <f t="shared" si="4"/>
-        <v>40000</v>
-      </c>
-      <c r="I10" s="11">
-        <f t="shared" si="4"/>
-        <v>286000</v>
-      </c>
-      <c r="J10" s="30">
-        <f>I10/H10</f>
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="14">
+    </row>
+    <row r="12" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="19">
         <v>14</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C12" s="20">
         <v>2000</v>
       </c>
-      <c r="D11" s="16">
-        <f>B11*C11</f>
+      <c r="D12" s="21">
+        <f t="shared" si="1"/>
         <v>28000</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E12" s="21">
         <v>26</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F12" s="20">
         <v>1000</v>
       </c>
-      <c r="G11" s="17">
-        <f>E11*F11</f>
+      <c r="G12" s="22">
+        <f t="shared" si="2"/>
         <v>26000</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H12" s="20">
         <f t="shared" si="4"/>
         <v>3000</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I12" s="22">
         <f t="shared" si="4"/>
         <v>54000</v>
       </c>
-      <c r="J11" s="31">
-        <f>I11/H11</f>
+      <c r="J12" s="36">
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K12" s="3">
         <v>14.12</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="30"/>
-    </row>
-    <row r="13" spans="1:12" s="46" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="46" t="s">
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="9">
+        <v>26</v>
+      </c>
+      <c r="C13" s="10">
+        <v>1800</v>
+      </c>
+      <c r="D13" s="11">
+        <f>B13*C13</f>
+        <v>46800</v>
+      </c>
+      <c r="E13" s="11">
+        <v>40</v>
+      </c>
+      <c r="F13" s="10">
+        <v>7200</v>
+      </c>
+      <c r="G13" s="12">
+        <f>E13*F13</f>
+        <v>288000</v>
+      </c>
+      <c r="H13" s="10">
+        <f t="shared" ref="H13" si="5">C13+F13</f>
+        <v>9000</v>
+      </c>
+      <c r="I13" s="12">
+        <f t="shared" ref="I13" si="6">D13+G13</f>
+        <v>334800</v>
+      </c>
+      <c r="J13" s="34">
+        <f>I13/H13</f>
+        <v>37.200000000000003</v>
+      </c>
+      <c r="K13" s="1">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="9">
+        <v>1.7</v>
+      </c>
+      <c r="C14" s="10">
+        <v>20000</v>
+      </c>
+      <c r="D14" s="11">
+        <f>B14*C14</f>
+        <v>34000</v>
+      </c>
+      <c r="E14" s="11">
+        <v>1.79</v>
+      </c>
+      <c r="F14" s="10">
         <v>0</v>
       </c>
-      <c r="B13" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="48" t="s">
+      <c r="G14" s="12">
+        <f>E14*F14</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="10">
+        <f t="shared" ref="H14" si="7">C14+F14</f>
+        <v>20000</v>
+      </c>
+      <c r="I14" s="12">
+        <f t="shared" ref="I14" si="8">D14+G14</f>
+        <v>34000</v>
+      </c>
+      <c r="J14" s="34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="49" t="s">
+      <c r="D15" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="49" t="s">
+      <c r="E15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="5">
+        <v>12.5</v>
+      </c>
+      <c r="C16" s="24">
+        <v>10000</v>
+      </c>
+      <c r="D16" s="25">
+        <v>11.3</v>
+      </c>
+      <c r="E16" s="7">
+        <f t="shared" ref="E16:E22" si="9">B16-D16</f>
+        <v>1.1999999999999993</v>
+      </c>
+      <c r="F16" s="7">
+        <f t="shared" ref="F16:F22" si="10">C16*E16</f>
+        <v>11999.999999999993</v>
+      </c>
+      <c r="G16" s="26">
+        <f t="shared" ref="G16:G22" si="11">E16/D16</f>
+        <v>0.10619469026548665</v>
+      </c>
+      <c r="H16" s="27"/>
+      <c r="I16" s="37">
+        <f t="shared" ref="I16:I22" si="12">B16*C16</f>
+        <v>125000</v>
+      </c>
+      <c r="J16" s="38"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="13">
+        <v>47.25</v>
+      </c>
+      <c r="C17" s="6">
+        <v>3000</v>
+      </c>
+      <c r="D17" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="9"/>
+        <v>15.75</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="10"/>
+        <v>47250</v>
+      </c>
+      <c r="G17" s="26">
+        <f t="shared" si="11"/>
+        <v>0.5</v>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="40">
+        <f t="shared" si="12"/>
+        <v>141750</v>
+      </c>
+      <c r="L17" s="27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="13">
+        <v>13.1</v>
+      </c>
+      <c r="C18" s="6">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="7">
+        <v>11.8</v>
+      </c>
+      <c r="E18" s="7">
+        <f t="shared" si="9"/>
+        <v>1.2999999999999989</v>
+      </c>
+      <c r="F18" s="7">
+        <f t="shared" si="10"/>
+        <v>3899.9999999999968</v>
+      </c>
+      <c r="G18" s="26">
+        <f t="shared" si="11"/>
+        <v>0.11016949152542363</v>
+      </c>
+      <c r="H18"/>
+      <c r="I18" s="40">
+        <f t="shared" si="12"/>
+        <v>39300</v>
+      </c>
+      <c r="J18" s="8"/>
+      <c r="K18"/>
+      <c r="L18"/>
+    </row>
+    <row r="19" spans="1:12" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="28">
+        <v>30</v>
+      </c>
+      <c r="C19" s="29">
+        <v>2000</v>
+      </c>
+      <c r="D19" s="25">
+        <v>24.9</v>
+      </c>
+      <c r="E19" s="21">
+        <f t="shared" si="9"/>
+        <v>5.1000000000000014</v>
+      </c>
+      <c r="F19" s="21">
+        <f t="shared" si="10"/>
+        <v>10200.000000000004</v>
+      </c>
+      <c r="G19" s="30">
+        <f t="shared" si="11"/>
+        <v>0.20481927710843381</v>
+      </c>
+      <c r="H19" s="31"/>
+      <c r="I19" s="40">
+        <f t="shared" si="12"/>
+        <v>60000</v>
+      </c>
+      <c r="J19" s="38"/>
+      <c r="L19" s="31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="5" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="28">
+        <v>9</v>
+      </c>
+      <c r="C20" s="29">
+        <v>10000</v>
+      </c>
+      <c r="D20" s="25">
+        <v>7.7</v>
+      </c>
+      <c r="E20" s="21">
+        <f t="shared" si="9"/>
+        <v>1.2999999999999998</v>
+      </c>
+      <c r="F20" s="21">
+        <f t="shared" si="10"/>
+        <v>12999.999999999998</v>
+      </c>
+      <c r="G20" s="30">
+        <f t="shared" si="11"/>
+        <v>0.1688311688311688</v>
+      </c>
+      <c r="H20" s="31"/>
+      <c r="I20" s="40">
+        <f t="shared" si="12"/>
+        <v>90000</v>
+      </c>
+      <c r="J20" s="38"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="C21" s="10">
+        <v>2000</v>
+      </c>
+      <c r="D21" s="11">
+        <v>10.9</v>
+      </c>
+      <c r="E21" s="11">
+        <f t="shared" si="9"/>
+        <v>0.59999999999999964</v>
+      </c>
+      <c r="F21" s="11">
+        <f t="shared" si="10"/>
+        <v>1199.9999999999993</v>
+      </c>
+      <c r="G21" s="32">
+        <f t="shared" si="11"/>
+        <v>5.5045871559632996E-2</v>
+      </c>
+      <c r="H21" s="33"/>
+      <c r="I21" s="41">
+        <f t="shared" si="12"/>
+        <v>23000</v>
+      </c>
+      <c r="J21" s="34"/>
+    </row>
+    <row r="22" spans="1:12" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="50"/>
-    </row>
-    <row r="14" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="19">
-        <v>12.5</v>
-      </c>
-      <c r="C14" s="20">
-        <v>10000</v>
-      </c>
-      <c r="D14" s="21">
-        <v>11.3</v>
-      </c>
-      <c r="E14" s="6">
-        <f t="shared" ref="E14:E18" si="5">B14-D14</f>
-        <v>1.1999999999999993</v>
-      </c>
-      <c r="F14" s="6">
-        <f t="shared" ref="F14:F18" si="6">C14*E14</f>
-        <v>11999.999999999993</v>
-      </c>
-      <c r="G14" s="22">
-        <f t="shared" ref="G14:G18" si="7">E14/D14</f>
-        <v>0.10619469026548665</v>
-      </c>
-      <c r="H14" s="23"/>
-      <c r="I14" s="32">
-        <f t="shared" ref="I14:I18" si="8">B14*C14</f>
-        <v>125000</v>
-      </c>
-      <c r="J14" s="33"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="8">
-        <v>48.25</v>
-      </c>
-      <c r="C15" s="9">
-        <v>3000</v>
-      </c>
-      <c r="D15" s="10">
-        <v>31.5</v>
-      </c>
-      <c r="E15" s="10">
-        <f t="shared" si="5"/>
-        <v>16.75</v>
-      </c>
-      <c r="F15" s="10">
-        <f t="shared" si="6"/>
-        <v>50250</v>
-      </c>
-      <c r="G15" s="39">
-        <f t="shared" si="7"/>
-        <v>0.53174603174603174</v>
-      </c>
-      <c r="H15" s="9"/>
-      <c r="I15" s="40">
-        <f t="shared" si="8"/>
-        <v>144750</v>
-      </c>
-      <c r="J15" s="30"/>
-      <c r="L15" s="41" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="12">
-        <v>13.1</v>
-      </c>
-      <c r="C16" s="5">
-        <v>3000</v>
-      </c>
-      <c r="D16" s="6">
-        <v>11.8</v>
-      </c>
-      <c r="E16" s="6">
-        <f t="shared" si="5"/>
-        <v>1.2999999999999989</v>
-      </c>
-      <c r="F16" s="6">
-        <f t="shared" si="6"/>
-        <v>3899.9999999999968</v>
-      </c>
-      <c r="G16" s="22">
-        <f t="shared" si="7"/>
-        <v>0.11016949152542363</v>
-      </c>
-      <c r="H16"/>
-      <c r="I16" s="34">
-        <f t="shared" si="8"/>
-        <v>39300</v>
-      </c>
-      <c r="J16" s="7"/>
-      <c r="K16"/>
-      <c r="L16"/>
-    </row>
-    <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="42">
-        <v>30</v>
-      </c>
-      <c r="C17" s="43">
-        <v>2000</v>
-      </c>
-      <c r="D17" s="21">
-        <v>24.9</v>
-      </c>
-      <c r="E17" s="16">
-        <f t="shared" si="5"/>
-        <v>5.1000000000000014</v>
-      </c>
-      <c r="F17" s="16">
-        <f t="shared" si="6"/>
-        <v>10200.000000000004</v>
-      </c>
-      <c r="G17" s="44">
-        <f t="shared" si="7"/>
-        <v>0.20481927710843381</v>
-      </c>
-      <c r="H17" s="45"/>
-      <c r="I17" s="34">
-        <f t="shared" si="8"/>
-        <v>60000</v>
-      </c>
-      <c r="J17" s="33"/>
-      <c r="L17" s="45" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="42">
-        <v>9</v>
-      </c>
-      <c r="C18" s="43">
-        <v>10000</v>
-      </c>
-      <c r="D18" s="21">
-        <v>7.7</v>
-      </c>
-      <c r="E18" s="16">
-        <f t="shared" si="5"/>
-        <v>1.2999999999999998</v>
-      </c>
-      <c r="F18" s="16">
-        <f t="shared" si="6"/>
-        <v>12999.999999999998</v>
-      </c>
-      <c r="G18" s="44">
-        <f t="shared" si="7"/>
-        <v>0.1688311688311688</v>
-      </c>
-      <c r="H18" s="45"/>
-      <c r="I18" s="34">
-        <f t="shared" si="8"/>
-        <v>90000</v>
-      </c>
-      <c r="J18" s="33"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="45" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="35"/>
-    </row>
-    <row r="20" spans="1:12" ht="15" x14ac:dyDescent="0.3">
-      <c r="A20" s="24"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="35"/>
+      <c r="B22" s="9">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="C22" s="10">
+        <v>2400</v>
+      </c>
+      <c r="D22" s="11">
+        <v>7.85</v>
+      </c>
+      <c r="E22" s="11">
+        <f t="shared" si="9"/>
+        <v>0.45000000000000107</v>
+      </c>
+      <c r="F22" s="11">
+        <f t="shared" si="10"/>
+        <v>1080.0000000000025</v>
+      </c>
+      <c r="G22" s="32">
+        <f t="shared" si="11"/>
+        <v>5.732484076433135E-2</v>
+      </c>
+      <c r="H22" s="33"/>
+      <c r="I22" s="41">
+        <f t="shared" si="12"/>
+        <v>19920</v>
+      </c>
+      <c r="J22" s="34"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="9">
+        <v>1.79</v>
+      </c>
+      <c r="C25" s="10">
+        <v>20000</v>
+      </c>
+      <c r="D25" s="21">
+        <v>1.7</v>
+      </c>
+      <c r="E25" s="21">
+        <f t="shared" ref="E25" si="13">B25-D25</f>
+        <v>9.000000000000008E-2</v>
+      </c>
+      <c r="F25" s="21">
+        <f t="shared" ref="F25" si="14">C25*E25</f>
+        <v>1800.0000000000016</v>
+      </c>
+      <c r="G25" s="30">
+        <f t="shared" ref="G25" si="15">E25/D25</f>
+        <v>5.2941176470588283E-2</v>
+      </c>
+      <c r="H25" s="43">
+        <v>46321</v>
+      </c>
+      <c r="I25" s="40">
+        <f t="shared" ref="I25" si="16">B25*C25</f>
+        <v>35800</v>
+      </c>
+      <c r="J25" s="36" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A14:L19">
-    <sortCondition ref="A14"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:L22">
+    <sortCondition ref="A16"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
